--- a/InputData/elec/MCF/Maximum Capacity Factor.xlsx
+++ b/InputData/elec/MCF/Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\MCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\KY\elec\MCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C769F5B2-C1AD-48F3-A825-C02B8D9F8A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAC87C19-795E-400C-A8C6-51F8AF1AAFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="17430" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>nuclear</t>
   </si>
@@ -118,9 +118,6 @@
     <t>This represents the maximum capacity factor a plant type can achieve</t>
   </si>
   <si>
-    <t>in any given hour. This is used for non-variable plant types. We apply</t>
-  </si>
-  <si>
     <t>a 5% penalty to represent that plants are not typically available 100% of the</t>
   </si>
   <si>
@@ -161,6 +158,12 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>in any given hour. This is used for non-variable plant types, including hydro. We apply</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
   </si>
 </sst>
 </file>
@@ -316,7 +319,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -336,6 +339,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -769,6 +773,12 @@
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45272</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G2" s="2"/>
@@ -778,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1"/>
       <c r="H3" s="1"/>
@@ -794,7 +804,7 @@
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1"/>
       <c r="H5" s="1"/>
@@ -802,7 +812,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1"/>
       <c r="H6" s="1"/>
@@ -824,24 +834,24 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -918,7 +928,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -978,7 +988,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0.95</v>
@@ -1032,7 +1042,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="3">
         <f>B2</f>
@@ -1041,7 +1051,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="3">
         <f>B4</f>
@@ -1050,7 +1060,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="3">
         <f>B10</f>
@@ -1059,7 +1069,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="3">
         <f>B14</f>
@@ -1068,7 +1078,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="3">
         <f>B5</f>
@@ -1077,7 +1087,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="3">
         <f>B4</f>
@@ -1086,7 +1096,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="3">
         <f>B4</f>

--- a/InputData/elec/MCF/Maximum Capacity Factor.xlsx
+++ b/InputData/elec/MCF/Maximum Capacity Factor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\KY\elec\MCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\MCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAC87C19-795E-400C-A8C6-51F8AF1AAFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF5E761-3510-4551-BBBD-14D4B578101B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="17430" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>nuclear</t>
   </si>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t>in any given hour. This is used for non-variable plant types, including hydro. We apply</t>
-  </si>
-  <si>
-    <t>Kentucky</t>
   </si>
 </sst>
 </file>
@@ -319,7 +316,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -339,7 +336,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -773,12 +769,6 @@
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45272</v>
-      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G2" s="2"/>
